--- a/tp_education_system/backend/services/exports/绩效工资审批表_2026年5月.xlsx
+++ b/tp_education_system/backend/services/exports/绩效工资审批表_2026年5月.xlsx
@@ -2237,8 +2237,7 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>据实填写，同意呈报。
-              （盖章）
-              2026年5月1日</t>
+              （盖章）</t>
         </is>
       </c>
       <c r="G1" s="7" t="n"/>
@@ -2329,9 +2328,21 @@
           <t>4、科员级</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n"/>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="33" t="n"/>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>1185</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>5925</t>
+        </is>
+      </c>
       <c r="E6" s="126" t="n"/>
       <c r="F6" s="127" t="inlineStr">
         <is>
@@ -2370,8 +2381,7 @@
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>（盖章）
-              2026年5月2日</t>
+          <t>（盖章）</t>
         </is>
       </c>
       <c r="D8" s="33" t="n"/>
@@ -2386,7 +2396,11 @@
         </is>
       </c>
       <c r="B9" s="32" t="n"/>
-      <c r="C9" s="40" t="n"/>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>1862</t>
+        </is>
+      </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="126" t="n"/>
       <c r="F9" s="41" t="n"/>
@@ -2402,9 +2416,21 @@
           <t>2、高级教师</t>
         </is>
       </c>
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="24" t="n"/>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>67012</t>
+        </is>
+      </c>
       <c r="E10" s="125" t="n"/>
       <c r="F10" s="130" t="inlineStr">
         <is>
@@ -2423,9 +2449,21 @@
           <t>3、一级教师</t>
         </is>
       </c>
-      <c r="B11" s="29" t="n"/>
-      <c r="C11" s="29" t="n"/>
-      <c r="D11" s="30" t="n"/>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>178024</t>
+        </is>
+      </c>
       <c r="E11" s="124" t="inlineStr">
         <is>
           <t>教育局意见</t>
@@ -2444,9 +2482,21 @@
           <t>4、二级教师</t>
         </is>
       </c>
-      <c r="B12" s="32" t="n"/>
-      <c r="C12" s="40" t="n"/>
-      <c r="D12" s="33" t="n"/>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>186150</t>
+        </is>
+      </c>
       <c r="E12" s="126" t="n"/>
       <c r="F12" s="41" t="n"/>
       <c r="K12" s="42" t="n"/>
@@ -2457,9 +2507,21 @@
           <t>5、三级教师</t>
         </is>
       </c>
-      <c r="B13" s="53" t="n"/>
-      <c r="C13" s="54" t="n"/>
-      <c r="D13" s="55" t="n"/>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C13" s="54" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="inlineStr">
+        <is>
+          <t>21432</t>
+        </is>
+      </c>
       <c r="E13" s="126" t="n"/>
       <c r="F13" s="41" t="n"/>
       <c r="K13" s="42" t="n"/>
@@ -2517,9 +2579,21 @@
           <t>2、技师</t>
         </is>
       </c>
-      <c r="B16" s="59" t="n"/>
-      <c r="C16" s="60" t="n"/>
-      <c r="D16" s="99" t="n"/>
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C16" s="60" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="D16" s="99" t="inlineStr">
+        <is>
+          <t>2662</t>
+        </is>
+      </c>
       <c r="E16" s="126" t="n"/>
       <c r="F16" s="41" t="n"/>
       <c r="K16" s="42" t="n"/>
@@ -2531,18 +2605,22 @@
         </is>
       </c>
       <c r="B17" s="63" t="n"/>
-      <c r="C17" s="63" t="n"/>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
       <c r="D17" s="64" t="n"/>
       <c r="E17" s="126" t="n"/>
       <c r="F17" s="41" t="inlineStr">
         <is>
           <t>根据相关文件及有关规定，经审核，同意你单位：
-                基础性绩效工资0人，0元；
-                生活补贴0人，0元；
-                合计0元；
-                岗位设置遗留0人，0元；
-                总计0元。
-                无乡镇补贴0人，。
+                基础性绩效工资357人，462311元；
+                生活补贴356人，124600元；
+                合计586911元；
+                岗位设置遗留2人，675.24元；
+                总计587586.24元。
+                无乡镇补贴1人，柯坤。
               2026年5月2日</t>
         </is>
       </c>
@@ -2555,7 +2633,11 @@
         </is>
       </c>
       <c r="B18" s="53" t="n"/>
-      <c r="C18" s="53" t="n"/>
+      <c r="C18" s="53" t="inlineStr">
+        <is>
+          <t>1185</t>
+        </is>
+      </c>
       <c r="D18" s="55" t="n"/>
       <c r="E18" s="126" t="n"/>
       <c r="F18" s="41" t="n"/>
@@ -2567,9 +2649,21 @@
           <t>5、初级工</t>
         </is>
       </c>
-      <c r="B19" s="53" t="n"/>
-      <c r="C19" s="54" t="n"/>
-      <c r="D19" s="55" t="n"/>
+      <c r="B19" s="53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="54" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="D19" s="55" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
       <c r="E19" s="125" t="n"/>
       <c r="F19" s="133" t="inlineStr">
         <is>
@@ -2613,9 +2707,17 @@
           <t>绩效工资合计</t>
         </is>
       </c>
-      <c r="B21" s="53" t="n"/>
+      <c r="B21" s="53" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
       <c r="C21" s="54" t="n"/>
-      <c r="D21" s="55" t="n"/>
+      <c r="D21" s="55" t="inlineStr">
+        <is>
+          <t>462311</t>
+        </is>
+      </c>
       <c r="E21" s="126" t="n"/>
       <c r="F21" s="73" t="inlineStr">
         <is>
@@ -2645,9 +2747,21 @@
           <t>乡镇补贴合计</t>
         </is>
       </c>
-      <c r="B22" s="53" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="55" t="n"/>
+      <c r="B22" s="53" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="C22" s="54" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="D22" s="55" t="inlineStr">
+        <is>
+          <t>124600</t>
+        </is>
+      </c>
       <c r="E22" s="126" t="n"/>
       <c r="F22" s="73" t="inlineStr">
         <is>
@@ -2677,9 +2791,21 @@
           <t>岗位设置遗留问题</t>
         </is>
       </c>
-      <c r="B23" s="59" t="n"/>
-      <c r="C23" s="60" t="n"/>
-      <c r="D23" s="99" t="n"/>
+      <c r="B23" s="59" t="inlineStr">
+        <is>
+          <t>李发金</t>
+        </is>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>321.3</t>
+        </is>
+      </c>
+      <c r="D23" s="99" t="inlineStr">
+        <is>
+          <t>321.3</t>
+        </is>
+      </c>
       <c r="E23" s="126" t="n"/>
       <c r="F23" s="77" t="inlineStr">
         <is>
@@ -2701,9 +2827,21 @@
           <t>岗位设置遗留问题</t>
         </is>
       </c>
-      <c r="B24" s="82" t="n"/>
-      <c r="C24" s="82" t="n"/>
-      <c r="D24" s="83" t="n"/>
+      <c r="B24" s="82" t="inlineStr">
+        <is>
+          <t>李发金</t>
+        </is>
+      </c>
+      <c r="C24" s="82" t="inlineStr">
+        <is>
+          <t>321.3</t>
+        </is>
+      </c>
+      <c r="D24" s="83" t="inlineStr">
+        <is>
+          <t>321.3</t>
+        </is>
+      </c>
       <c r="E24" s="126" t="n"/>
       <c r="F24" s="73" t="inlineStr">
         <is>
@@ -2733,9 +2871,17 @@
           <t>岗位设置遗留问题合计</t>
         </is>
       </c>
-      <c r="B25" s="85" t="n"/>
+      <c r="B25" s="85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C25" s="85" t="n"/>
-      <c r="D25" s="86" t="n"/>
+      <c r="D25" s="86" t="inlineStr">
+        <is>
+          <t>675.24</t>
+        </is>
+      </c>
       <c r="E25" s="126" t="n"/>
       <c r="F25" s="77" t="inlineStr">
         <is>
@@ -2758,7 +2904,11 @@
           <t>退休干部</t>
         </is>
       </c>
-      <c r="B26" s="88" t="n"/>
+      <c r="B26" s="88" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
       <c r="C26" s="89" t="n"/>
       <c r="D26" s="90" t="n"/>
       <c r="E26" s="126" t="n"/>
@@ -2788,7 +2938,11 @@
           <t>退休工人</t>
         </is>
       </c>
-      <c r="B27" s="94" t="n"/>
+      <c r="B27" s="94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C27" s="105" t="n"/>
       <c r="D27" s="96" t="n"/>
       <c r="E27" s="126" t="n"/>
@@ -2802,7 +2956,11 @@
           <t>离休干部</t>
         </is>
       </c>
-      <c r="B28" s="98" t="n"/>
+      <c r="B28" s="98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C28" s="59" t="n"/>
       <c r="D28" s="99" t="n"/>
       <c r="E28" s="126" t="n"/>
@@ -2812,7 +2970,7 @@
     <row r="29" ht="25" customFormat="1" customHeight="1" s="13">
       <c r="A29" s="100" t="inlineStr">
         <is>
-          <t>备注：</t>
+          <t>备注：1.高级教师调离1人：测试教师2.二级教师返聘1人：李恩源3.二级教师退休1人：李恩源</t>
         </is>
       </c>
       <c r="B29" s="101" t="n">
